--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128753674</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128753674</v>
+        <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>92220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Skråmträsk, Östra Skråmträsk, Vb</t>
+          <t>Selasberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768684</v>
+        <v>769388</v>
       </c>
       <c r="R2" t="n">
-        <v>7182006</v>
+        <v>7182237</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,11 +763,6 @@
       </c>
       <c r="AE2" t="b">
         <v>0</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>barcode</t>
-        </is>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -775,15 +770,4941 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134652317</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>769226</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7182065</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134652318</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>658</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>769186</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7182078</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134652332</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>768953</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7182029</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134652336</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92245</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>658</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>768956</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7181997</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134652319</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>769186</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7182078</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134652321</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>769135</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7182088</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134652322</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>769084</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7182115</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134652325</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>769004</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7182007</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134652329</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>768989</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7182022</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134652334</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>768947</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7182032</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134652345</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>768919</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7182132</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134652301</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92406</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>769131</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7182207</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bilder, på björk</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Rätt hård björklåga, där nävret separerat och börjat lossna från veden. Rynkskinn hittades inte på någon av granlågorna i området, och björklågan där den växte hade inte kontakt med någon granlåga</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Betula # Rätt hård björklåga, där nävret separerat och börjat lossna från veden. Rynkskinn hittades inte på någon av granlågorna i området, och björklågan där den växte hade inte kontakt med någon granlåga</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134652293</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92153</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>769363</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7182180</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134652316</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91896</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>769195</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7182161</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134652295</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92385</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>769351</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7182191</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134652315</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>769181</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7182190</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134652324</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>768993</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7182010</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134652343</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91937</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>768932</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7182065</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134652287</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>769483</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7182111</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134652289</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>769482</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7182149</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134652290</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>769441</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7182201</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134652292</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>769390</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7182202</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134652294</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>769357</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7182193</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134652299</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>769371</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7182143</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134652303</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>769336</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7182235</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134652305</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>769520</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7182239</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134652312</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>769192</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7182176</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134652327</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>769000</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7182024</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134652338</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>768949</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7182014</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Barksprätt Bild 1047</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134652297</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>769366</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7182158</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134652304</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>769354</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7182231</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128753674</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Östra Skråmträsk, Östra Skråmträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>768684</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7182006</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
           <t>Johan Olofsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>Johan Olofsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134652323</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>769021</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7182002</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134652330</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>768959</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7182027</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bild 2</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134652331</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>768957</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7182036</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134652333</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>768945</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7182041</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134652335</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>768943</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7182019</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134652337</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>768943</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7182004</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134652339</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>768934</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7182006</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134652340</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>768925</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7182026</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134652341</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>768909</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7182039</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134652342</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>768930</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7182047</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134652344</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>768930</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7182075</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134652355</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>768690</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7182039</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134652300</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>769319</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7182064</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652291</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652317</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652318</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652332</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652336</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652319</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652321</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652322</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652325</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652329</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652334</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652345</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2092,6 +2157,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652301</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2204,6 +2274,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652293</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2311,6 +2386,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652316</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2423,6 +2503,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652295</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2530,6 +2615,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652315</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2637,6 +2727,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652324</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2744,6 +2839,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652343</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2851,6 +2951,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652287</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2958,6 +3063,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652289</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3065,6 +3175,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652290</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3172,6 +3287,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652292</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3279,6 +3399,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652294</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3386,6 +3511,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652299</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3493,6 +3623,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652303</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3600,6 +3735,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652305</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3707,6 +3847,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652312</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3827,6 +3972,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652327</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3947,6 +4097,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652338</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4067,6 +4222,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652297</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4187,6 +4347,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652304</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4299,6 +4464,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128753674</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4411,6 +4581,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652323</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4523,6 +4698,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652330</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4635,6 +4815,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652331</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4742,6 +4927,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652333</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4849,6 +5039,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652335</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4956,6 +5151,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652337</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5063,6 +5263,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652339</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5170,6 +5375,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652340</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5277,6 +5487,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652341</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5384,6 +5599,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652342</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5491,6 +5711,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652344</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5598,6 +5823,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652355</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5705,8 +5935,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652300</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128753674</v>
+        <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östra Skråmträsk, Östra Skråmträsk, Vb</t>
+          <t>Selasberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768684</v>
+        <v>769388</v>
       </c>
       <c r="R2" t="n">
-        <v>7182006</v>
+        <v>7182237</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig förekomst.</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,11 +768,6 @@
       </c>
       <c r="AE2" t="b">
         <v>0</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>barcode</t>
-        </is>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -780,24 +775,5400 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652291</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134652317</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>769226</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7182065</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652317</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134652318</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92319</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>658</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>769186</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7182078</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652318</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134652332</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92319</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>768953</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7182029</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652332</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134652336</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92319</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>658</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>768956</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7181997</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652336</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134652319</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>769186</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7182078</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652319</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134652321</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>769135</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7182088</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652321</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134652322</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>769084</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7182115</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652322</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134652325</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>769004</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7182007</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652325</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134652329</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>768989</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7182022</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652329</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134652334</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>768947</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7182032</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652334</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134652345</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>768919</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7182132</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652345</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134652301</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92480</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>769131</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7182207</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bilder, på björk</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Rätt hård björklåga, där nävret separerat och börjat lossna från veden. Rynkskinn hittades inte på någon av granlågorna i området, och björklågan där den växte hade inte kontakt med någon granlåga</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Betula # Rätt hård björklåga, där nävret separerat och börjat lossna från veden. Rynkskinn hittades inte på någon av granlågorna i området, och björklågan där den växte hade inte kontakt med någon granlåga</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652301</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134652293</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92227</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>769363</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7182180</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652293</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134652316</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91970</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>769195</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7182161</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652316</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134652295</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92459</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>769351</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7182191</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bild</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652295</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134652315</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>769181</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7182190</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652315</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134652324</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>768993</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7182010</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652324</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134652343</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>768932</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7182065</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652343</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134652287</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>769483</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7182111</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652287</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134652289</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>769482</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7182149</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652289</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134652290</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>769441</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7182201</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652290</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134652292</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>769390</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7182202</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652292</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134652294</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>769357</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7182193</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652294</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134652299</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>769371</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7182143</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652299</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134652303</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>769336</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7182235</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652303</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134652305</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>769520</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7182239</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652305</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134652312</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>769192</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7182176</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652312</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134652327</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>769000</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7182024</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652327</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134652338</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>768949</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7182014</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Barksprätt Bild 1047</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652338</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134652297</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>769366</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7182158</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652297</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134652304</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>769354</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7182231</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652304</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128753674</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Östra Skråmträsk, Östra Skråmträsk, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>768684</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7182006</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig förekomst.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
           <t>Johan Olofsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>Johan Olofsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128753674</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134652323</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>769021</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7182002</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652323</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134652330</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>768959</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7182027</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bild 2</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652330</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134652331</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>768957</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7182036</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bild 3</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652331</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134652333</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>768945</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7182041</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652333</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134652335</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>768943</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7182019</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652335</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134652337</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>768943</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7182004</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652337</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134652339</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>768934</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7182006</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652339</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134652340</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>768925</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7182026</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652340</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134652341</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>768909</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7182039</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652341</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134652342</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>768930</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7182047</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652342</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134652344</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>768930</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7182075</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652344</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134652355</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>768690</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7182039</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652355</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134652300</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Selasberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>769319</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7182064</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skellefteå socken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134652300</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92459</v>
+        <v>92461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652317</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92461</v>
+        <v>92475</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>134652287</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>134652289</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>134652290</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>134652292</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>134652294</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>134652299</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>134652303</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>134652305</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>134652312</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>134652327</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>134652338</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>134652297</v>
       </c>
       <c r="B32" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>134652304</v>
       </c>
       <c r="B33" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>134652300</v>
       </c>
       <c r="B47" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652317</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>91986</v>
+        <v>91987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92475</v>
+        <v>92476</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>134652287</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>134652289</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>134652290</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>134652292</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>134652294</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>134652299</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>134652303</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>134652305</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>134652312</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>134652300</v>
       </c>
       <c r="B47" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>91987</v>
+        <v>91988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92476</v>
+        <v>92477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652317</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>91988</v>
+        <v>91989</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92477</v>
+        <v>92478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>134652287</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>134652289</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>134652290</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>134652292</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>134652294</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>134652299</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>134652303</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>134652305</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>134652312</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>134652327</v>
       </c>
       <c r="B30" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>134652338</v>
       </c>
       <c r="B31" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>134652297</v>
       </c>
       <c r="B32" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>134652304</v>
       </c>
       <c r="B33" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>134652300</v>
       </c>
       <c r="B47" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652317</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>91989</v>
+        <v>91995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92478</v>
+        <v>92484</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>134652287</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>134652289</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>134652290</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>134652292</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>134652294</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>134652299</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>134652303</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>134652305</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>134652312</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>134652327</v>
       </c>
       <c r="B30" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>134652338</v>
       </c>
       <c r="B31" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>134652297</v>
       </c>
       <c r="B32" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>134652304</v>
       </c>
       <c r="B33" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>134652300</v>
       </c>
       <c r="B47" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652317</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>91995</v>
+        <v>91996</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92484</v>
+        <v>92485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>134652287</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>134652289</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>134652290</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>134652292</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>134652294</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>134652299</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>134652303</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>134652305</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>134652312</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>134652327</v>
       </c>
       <c r="B30" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>134652338</v>
       </c>
       <c r="B31" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>134652297</v>
       </c>
       <c r="B32" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>134652304</v>
       </c>
       <c r="B33" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>134652300</v>
       </c>
       <c r="B47" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652317</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>91996</v>
+        <v>92002</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92485</v>
+        <v>92491</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>134652287</v>
       </c>
       <c r="B21" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>134652289</v>
       </c>
       <c r="B22" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>134652290</v>
       </c>
       <c r="B23" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>134652292</v>
       </c>
       <c r="B24" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>134652294</v>
       </c>
       <c r="B25" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>134652299</v>
       </c>
       <c r="B26" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>134652303</v>
       </c>
       <c r="B27" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>134652305</v>
       </c>
       <c r="B28" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>134652312</v>
       </c>
       <c r="B29" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>134652300</v>
       </c>
       <c r="B47" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>134652317</v>
       </c>
       <c r="B3" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>92002</v>
+        <v>92009</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92491</v>
+        <v>92498</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>134652287</v>
       </c>
       <c r="B21" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>134652289</v>
       </c>
       <c r="B22" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>134652290</v>
       </c>
       <c r="B23" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>134652292</v>
       </c>
       <c r="B24" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>134652294</v>
       </c>
       <c r="B25" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>134652299</v>
       </c>
       <c r="B26" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>134652303</v>
       </c>
       <c r="B27" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>134652305</v>
       </c>
       <c r="B28" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>134652312</v>
       </c>
       <c r="B29" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>134652327</v>
       </c>
       <c r="B30" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>134652338</v>
       </c>
       <c r="B31" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         <v>134652297</v>
       </c>
       <c r="B32" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>134652304</v>
       </c>
       <c r="B33" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>134652300</v>
       </c>
       <c r="B47" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 22797-2026 artfynd.xlsx
+++ b/artfynd/A 22797-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134652291</v>
       </c>
       <c r="B2" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>134652318</v>
       </c>
       <c r="B4" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>134652332</v>
       </c>
       <c r="B5" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>134652336</v>
       </c>
       <c r="B6" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>134652319</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>134652321</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>134652322</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>134652325</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>134652329</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>134652334</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>134652345</v>
       </c>
       <c r="B13" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>134652301</v>
       </c>
       <c r="B14" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>134652293</v>
       </c>
       <c r="B15" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>134652316</v>
       </c>
       <c r="B16" t="n">
-        <v>92009</v>
+        <v>92010</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>134652295</v>
       </c>
       <c r="B17" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>134652315</v>
       </c>
       <c r="B18" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>134652324</v>
       </c>
       <c r="B19" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>134652343</v>
       </c>
       <c r="B20" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>134652323</v>
       </c>
       <c r="B35" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>134652330</v>
       </c>
       <c r="B36" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>134652331</v>
       </c>
       <c r="B37" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>134652333</v>
       </c>
       <c r="B38" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>134652335</v>
       </c>
       <c r="B39" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>134652337</v>
       </c>
       <c r="B40" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>134652339</v>
       </c>
       <c r="B41" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>134652340</v>
       </c>
       <c r="B42" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>134652341</v>
       </c>
       <c r="B43" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>134652342</v>
       </c>
       <c r="B44" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>134652344</v>
       </c>
       <c r="B45" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>134652355</v>
       </c>
       <c r="B46" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
